--- a/output/full_scan/batch_seq1_2026-06-12.xlsx
+++ b/output/full_scan/batch_seq1_2026-06-12.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1090.03173396883</v>
+        <v>1135.03173396883</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>36.75</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>81.27599539485402</v>
+        <v>81.27599564041908</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.92511758534484</v>
+        <v>25.9251176877819</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.003173396883055</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.4397527106238872</v>
+        <v>0.4397527103949348</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>986.9806013947656</v>
+        <v>1041.980601394766</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>117.5</v>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>77.44677338759767</v>
+        <v>77.44677346665196</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>33.1071559642257</v>
+        <v>33.10715610735372</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.198060139476567</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.052725832369829</v>
+        <v>2.052725831911935</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>985</v>
+        <v>1040</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>45.1</v>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>75.34149983512154</v>
+        <v>75.34149988672739</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>28.82415598857462</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.251871130569536</v>
+        <v>0.2518711305313766</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>1303</v>
+        <v>1210</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>962.2597851827406</v>
+        <v>1013.688196939389</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>106.5</v>
+        <v>55.3</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>59.96896731457674</v>
+        <v>65.30535028409007</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>21.69554149485376</v>
+        <v>25.42507422001356</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.7259785182740691</v>
+        <v>0.8688196939388666</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.1830684422029689</v>
+        <v>0.3375643945332581</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>1210</v>
+        <v>1303</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>958.6881969393888</v>
+        <v>1002.259785182741</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>55.3</v>
+        <v>106.5</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,29 +764,29 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>65.30535030832409</v>
+        <v>59.96896732732178</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>25.42507418283904</v>
+        <v>21.69554152577097</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.8688196939388666</v>
+        <v>0.7259785182740691</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.3375643944760139</v>
+        <v>-0.1830684423174342</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>925.0473963272452</v>
+        <v>940.0473963272452</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>9.99</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>73.77240666589485</v>
+        <v>73.77240671559562</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>39.73154938835202</v>
+        <v>39.73154933967556</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>1.004739632724513</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.142512199181277</v>
+        <v>0.1425121991621971</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -856,7 +856,7 @@
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>898.0798641947557</v>
+        <v>933.0798641947556</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>76.5</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>65.54302450797954</v>
+        <v>65.54302455340495</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>17.37630779630129</v>
+        <v>17.37630778218497</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.8079864194755747</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.342317707488412</v>
+        <v>0.3423177074502522</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>897.9539344256567</v>
+        <v>932.9539344256568</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>29.1</v>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.0612376811271</v>
+        <v>57.06123770002851</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>20.8061775671915</v>
+        <v>20.80617756301977</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>0.7953934425656742</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1331567918992182</v>
+        <v>0.1331567918896805</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -951,21 +951,21 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>1442</v>
+        <v>1225</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>名軒</t>
+          <t>福懋油</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>883.2927516572607</v>
+        <v>890.5928904527116</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>27.95</v>
+        <v>31.15</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>57.59880745718282</v>
+        <v>56.51591114192767</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>17.45191335670691</v>
+        <v>15.26224010161954</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.829275165726073</v>
+        <v>2.55928904527116</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.1617996750000256</v>
+        <v>0.2115242250217246</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>聯華食</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>859.3565662876673</v>
+        <v>889.8503100599576</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>89.09999999999999</v>
+        <v>150.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.35935493014458</v>
+        <v>62.22385173386225</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>18.81570825842492</v>
+        <v>15.18549819447347</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9356566287667276</v>
+        <v>1.985031005995759</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.3570931269506637</v>
+        <v>0.2885557349629289</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>1225</v>
+        <v>1231</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>福懋油</t>
+          <t>聯華食</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>855.5928904527116</v>
+        <v>874.3565662876673</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>31.15</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,16 +1082,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>56.51591114192767</v>
+        <v>60.35935477719108</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>15.26224010161954</v>
+        <v>18.81570815192847</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2.55928904527116</v>
+        <v>0.9356566287667276</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2115242250217246</v>
+        <v>0.3570931262828817</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>1232</v>
+        <v>1444</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>力麗</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>854.8503100599576</v>
+        <v>859.0957573481872</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>150.5</v>
+        <v>7.25</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>62.22385184924924</v>
+        <v>64.68694841925691</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>15.18549818942959</v>
+        <v>34.5635150307038</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.985031005995759</v>
+        <v>0.909575734818728</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.2885557347721592</v>
+        <v>0.07357096735229331</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>1568</v>
+        <v>1321</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>倉佑</t>
+          <t>大洋</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>842.8162389770087</v>
+        <v>854.5691962413143</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>39.65</v>
+        <v>31.75</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>55.90527183492902</v>
+        <v>66.62596890908952</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>48.54523830748323</v>
+        <v>42.88505644334163</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.2816238977008674</v>
+        <v>1.956919624131433</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>-0.7321316197888557</v>
+        <v>0.4049874669883607</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>宏和</t>
+          <t>名軒</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>827.8003892044867</v>
+        <v>853.2927516572607</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>16.8</v>
+        <v>27.95</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>65.12986099025127</v>
+        <v>57.59880755329355</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>25.6797750406827</v>
+        <v>17.45191312224214</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.780038920448674</v>
+        <v>1.829275165726073</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>1</v>
@@ -1259,11 +1259,11 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.1066444392358204</v>
+        <v>0.1617996744276411</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>811.6724980361555</v>
+        <v>846.6724980361555</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>29.2</v>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>64.57215269513709</v>
+        <v>64.57215286708481</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33.05991564825663</v>
+        <v>33.05991567982002</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>0.667249803615545</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.1700146865188079</v>
+        <v>0.1700146864234123</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>1101</v>
+        <v>1568</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台泥</t>
+          <t>倉佑</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>804.1064461226964</v>
+        <v>842.8162389770087</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>24.55</v>
+        <v>39.65</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>53.44594783283974</v>
+        <v>55.90527183492902</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>12.28757046895432</v>
+        <v>48.54523830748323</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.9106446122696398</v>
+        <v>0.2816238977008674</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.0143965613956595</v>
+        <v>-0.7321316197888557</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>力麗</t>
+          <t>宏和</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>804.0957573481872</v>
+        <v>842.8003892044867</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>7.25</v>
+        <v>16.8</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>64.68694839163209</v>
+        <v>65.12986097033651</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>34.56351502510857</v>
+        <v>25.67977510197458</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.909575734818728</v>
+        <v>1.780038920448674</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.0735709673828204</v>
+        <v>0.1066444390927268</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>1321</v>
+        <v>1532</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>大洋</t>
+          <t>勤美</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>799.5691962413143</v>
+        <v>834.0987354062075</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>31.75</v>
+        <v>23.4</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>66.62596894039879</v>
+        <v>75.70312109765203</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>42.88505642620584</v>
+        <v>34.20647048561394</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.956919624131433</v>
+        <v>1.409873540620754</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>1</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.4049874670551374</v>
+        <v>0.2452617533730501</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>1532</v>
+        <v>1101</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>勤美</t>
+          <t>台泥</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>779.0987354062075</v>
+        <v>804.1064461226964</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>23.4</v>
+        <v>24.55</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,49 +1506,49 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>75.7031208321627</v>
+        <v>53.44594786398757</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>34.20647047874464</v>
+        <v>12.28757053642108</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.409873540620754</v>
+        <v>0.9106446122696398</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.2452617535829245</v>
+        <v>0.0143965613479611</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>1434</v>
+        <v>1339</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>福懋</t>
+          <t>昭輝</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>757.8153030032984</v>
+        <v>794.8266485384092</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>16.65</v>
+        <v>44.8</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.86234272720476</v>
+        <v>62.64266407429002</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>25.45221563647311</v>
+        <v>27.67264962932727</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7815303003298349</v>
+        <v>0.4826648538409245</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.1318642686414223</v>
+        <v>0.1200411360157023</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>1339</v>
+        <v>1434</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>昭輝</t>
+          <t>福懋</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>754.8266485384092</v>
+        <v>792.8153030032984</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>44.8</v>
+        <v>16.65</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>62.64266394779362</v>
+        <v>61.86234272720476</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.67264947938874</v>
+        <v>25.45221566443669</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4826648538409245</v>
+        <v>0.7815303003298349</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.1200411363305128</v>
+        <v>0.1318642686223436</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>1409</v>
+        <v>1319</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>新纖</t>
+          <t>東陽</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>753.6988183375375</v>
+        <v>776.753238343731</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>25.5</v>
+        <v>99.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>63.71588029553638</v>
+        <v>62.73588267961885</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>39.09181349561165</v>
+        <v>33.14855208108663</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3698818337537559</v>
+        <v>0.6753238343731077</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,11 +1683,11 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.07024466649473381</v>
+        <v>1.332163915244758</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1704,7 @@
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>753.3293588023566</v>
+        <v>768.3293588023566</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>29.65</v>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>62.74000616364423</v>
+        <v>62.74000633345485</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>27.34831864940229</v>
+        <v>27.34831867805151</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.8329358802356582</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1626265005433952</v>
+        <v>0.1626265004479976</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>東陽</t>
+          <t>上曜</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>741.753238343731</v>
+        <v>766.6918228723578</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>99.5</v>
+        <v>11.3</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>62.73588269082989</v>
+        <v>59.71891296455229</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>33.14855197891868</v>
+        <v>19.79530556599291</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.6753238343731077</v>
+        <v>1.669182287235776</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>1.332163915340156</v>
+        <v>0.1384458313480276</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>1316</v>
+        <v>1409</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>上曜</t>
+          <t>新纖</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>711.6918228723578</v>
+        <v>753.6988183375375</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>11.3</v>
+        <v>25.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>59.7189127589742</v>
+        <v>63.71588029553638</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>19.79530561185067</v>
+        <v>39.09181349561165</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.669182287235776</v>
+        <v>0.3698818337537559</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>1</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.1384458314815825</v>
+        <v>0.07024466649473381</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>1438</v>
+        <v>1506</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>三地開發</t>
+          <t>正道</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>705</v>
+        <v>738.5760827426565</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>24.05</v>
+        <v>10.4</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>66.90497843051233</v>
+        <v>51.46738483571314</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>33.12439796368675</v>
+        <v>22.7495016029955</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>5.482856821024114</v>
+        <v>1.857608274265644</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.6648491663332965</v>
+        <v>0.0375288591607055</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>1506</v>
+        <v>1533</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>正道</t>
+          <t>車王電</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>703.5760827426565</v>
+        <v>733.9090966263775</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>10.4</v>
+        <v>38.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>51.4673848662469</v>
+        <v>56.96430166536023</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>22.74950179888486</v>
+        <v>53.6993516768644</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.857608274265644</v>
+        <v>0.3909096626377498</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.0375288592179441</v>
+        <v>-0.3065736101876892</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>1463</v>
+        <v>1438</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>強盛新</t>
+          <t>三地開發</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>698.6966846174178</v>
+        <v>720</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>17.8</v>
+        <v>24.05</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>48.23796180873901</v>
+        <v>66.90497842752448</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>9.742481827850082</v>
+        <v>33.12439798991442</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.8696684617417735</v>
+        <v>5.482856821024114</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.0061389097887342</v>
+        <v>0.6648491663523755</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>1102</v>
+        <v>1463</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>亞泥</t>
+          <t>強盛新</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>696.1642126938193</v>
+        <v>718.6966846174178</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>35.2</v>
+        <v>17.8</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.60133823197846</v>
+        <v>48.23796189141725</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>12.73122479841598</v>
+        <v>9.742481846447246</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6164212693819328</v>
+        <v>0.8696684617417735</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.166180131068957</v>
+        <v>0.006138909741039</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>1533</v>
+        <v>1102</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>車王電</t>
+          <t>亞泥</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>693.9090966263775</v>
+        <v>711.1642126938193</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>38.5</v>
+        <v>35.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,49 +2089,49 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>56.96430161388111</v>
+        <v>58.6013381043597</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>53.69935143116459</v>
+        <v>12.73122486333622</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3909096626377498</v>
+        <v>0.6164212693819328</v>
       </c>
       <c r="K31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.3065736099968981</v>
+        <v>0.1661801311357289</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>1229</v>
+        <v>1513</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>聯華</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>684.0065604361404</v>
+        <v>698.456123908084</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>41.65</v>
+        <v>167</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.57009585234214</v>
+        <v>53.22649545980878</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>27.46515374757823</v>
+        <v>25.62059293887097</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4006560436140385</v>
+        <v>0.3456123908084035</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1895627717347227</v>
+        <v>-0.7746001194299614</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>1513</v>
+        <v>1229</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>聯華</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>678.456123908084</v>
+        <v>684.0065604361404</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>167</v>
+        <v>41.65</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>53.22649542298301</v>
+        <v>52.57009586969648</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.62059280302861</v>
+        <v>27.46515377154916</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.3456123908084035</v>
+        <v>0.4006560436140385</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,11 +2213,11 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-0.7746001186667728</v>
+        <v>0.1895627715343883</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2276,21 +2276,21 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>1314</v>
+        <v>1475</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>中石化</t>
+          <t>業旺</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>670.7926439297082</v>
+        <v>662.9412424523239</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>7.84</v>
+        <v>27.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.13449033468745</v>
+        <v>59.93602292916615</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>15.05815542589584</v>
+        <v>29.18718301008352</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5792643929708198</v>
+        <v>0.2941242452323881</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0605313806710821</v>
+        <v>0.3350752290810167</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>1432</v>
+        <v>1314</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>大魯閣</t>
+          <t>中石化</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>667.4402712451008</v>
+        <v>655.7926439297082</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>17.35</v>
+        <v>7.84</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>61.92871822211917</v>
+        <v>57.13449036966683</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>23.64187216224361</v>
+        <v>15.05815547466847</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.7440271245100817</v>
+        <v>0.5792643929708198</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0957766332580543</v>
+        <v>0.0605313806462794</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>1103</v>
+        <v>1432</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>嘉泥</t>
+          <t>大魯閣</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>643.397976990559</v>
+        <v>652.4402712451008</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>13.55</v>
+        <v>17.35</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>55.71538813832423</v>
+        <v>61.9287183502943</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>14.93298875418853</v>
+        <v>23.64187234762576</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.8397976990559013</v>
+        <v>0.7440271245100817</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0363806980306438</v>
+        <v>0.09577663319127699</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>1530</v>
+        <v>1537</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>亞崴</t>
+          <t>廣隆</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>642.6650102225093</v>
+        <v>650.4659577436787</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>30.6</v>
+        <v>127</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>50.79933889433035</v>
+        <v>56.73316543913896</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.02661962349327</v>
+        <v>11.99408054009265</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.2665010222509266</v>
+        <v>0.5465957743678648</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.363451370169912</v>
+        <v>0.0190232407357145</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>1203</v>
+        <v>1313</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>味王</t>
+          <t>聯成</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>642.0062891595683</v>
+        <v>648.5536300397275</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>42.8</v>
+        <v>11.25</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.08312145469189</v>
+        <v>53.38496362879346</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>23.72536017588285</v>
+        <v>17.98254353509649</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7006289159568225</v>
+        <v>0.8553630039727513</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.1023070560911772</v>
+        <v>0.0655820041663597</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>1537</v>
+        <v>1103</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>廣隆</t>
+          <t>嘉泥</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>630.4659577436787</v>
+        <v>643.397976990559</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>127</v>
+        <v>13.55</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>56.73316552774544</v>
+        <v>55.715388209718</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11.99408048892513</v>
+        <v>14.9329887570819</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5465957743678648</v>
+        <v>0.8397976990559013</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0190232409265044</v>
+        <v>0.0363806979924846</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>1313</v>
+        <v>1531</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>聯成</t>
+          <t>高林股</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>628.5536300397275</v>
+        <v>641.3214552816202</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>11.25</v>
+        <v>13</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.38496359954461</v>
+        <v>58.42552220904462</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>17.98254358865696</v>
+        <v>20.16215183842409</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8553630039727513</v>
+        <v>1.132145528162012</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.0655820042045188</v>
+        <v>0.0790968227358078</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>1110</v>
+        <v>1236</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>東泥</t>
+          <t>宏亞</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>628.3004896690938</v>
+        <v>639.6518813957736</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>15.45</v>
+        <v>25.7</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>58.10218566376773</v>
+        <v>62.64081967150266</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>29.31634337834959</v>
+        <v>15.63128038809612</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3300489669093865</v>
+        <v>0.9651881395773561</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.107196935917916</v>
+        <v>0.1928231011864686</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>1475</v>
+        <v>1341</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>業旺</t>
+          <t>富林-KY</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>627.9412424523239</v>
+        <v>630.1625566180171</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>27.2</v>
+        <v>62.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>59.9360231607795</v>
+        <v>52.00754720404093</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>29.18718302425616</v>
+        <v>13.27798935396898</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.2941242452323881</v>
+        <v>1.516255661801711</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.3350752289760812</v>
+        <v>-0.0705377349032191</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>1531</v>
+        <v>1256</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>高林股</t>
+          <t>鮮活果汁-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>626.3214552816202</v>
+        <v>628.1096068583381</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>13</v>
+        <v>178</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>58.42552207925973</v>
+        <v>45.85965482411567</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.16215183563548</v>
+        <v>28.25635863673932</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.132145528162012</v>
+        <v>0.3109606858338057</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.07909682277396821</v>
+        <v>-3.561089200151376</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>1236</v>
+        <v>1414</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>宏亞</t>
+          <t>東和</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>624.6518813957736</v>
+        <v>626.8464251455313</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>25.7</v>
+        <v>16.8</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>62.64081988820182</v>
+        <v>58.02488473290008</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>15.63128039780005</v>
+        <v>28.36879206438177</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.9651881395773561</v>
+        <v>0.184642514553125</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1928231011387661</v>
+        <v>0.2434468810386653</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>1456</v>
+        <v>1326</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>怡華</t>
+          <t>台化</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>615.7028566477787</v>
+        <v>626.5336044077791</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>14.2</v>
+        <v>48.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>59.50271454829452</v>
+        <v>50.1375522656016</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>17.29317344978797</v>
+        <v>22.19151716392629</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.570285664777872</v>
+        <v>0.653360440777913</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,11 +2902,11 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.1438837593515702</v>
+        <v>-0.3172928980582552</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>599.3536631682599</v>
+        <v>619.3536631682599</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>224</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>51.17404325013394</v>
+        <v>51.17404357051986</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>21.99356500502688</v>
+        <v>21.99356508401756</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>0.4353663168259917</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.8182767051329589</v>
+        <v>0.8182767024617985</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2965,21 +2965,21 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>1413</v>
+        <v>1436</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>宏洲</t>
+          <t>華友聯</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>591.5605107125969</v>
+        <v>615.7872571453696</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>9.58</v>
+        <v>46.4</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.36503943886717</v>
+        <v>48.52710990479744</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>5.554012744073292</v>
+        <v>33.17138065577204</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.156051071259685</v>
+        <v>1.078725714536963</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>1</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.006574718668134</v>
+        <v>0.3986082664756589</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>1341</v>
+        <v>1504</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>富林-KY</t>
+          <t>東元</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>590.1625566180171</v>
+        <v>612.7620363517715</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>62.1</v>
+        <v>71</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,49 +3043,49 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>52.00754733569675</v>
+        <v>48.23711723844935</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>13.27798934177428</v>
+        <v>26.64561306135338</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.516255661801711</v>
+        <v>0.2762036351771496</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0705377350940093</v>
+        <v>-1.047308004321788</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>1503</v>
+        <v>1530</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>亞崴</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>589.0755798604765</v>
+        <v>612.6650102225093</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>220</v>
+        <v>30.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.39507429785147</v>
+        <v>50.79933897848655</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>24.90189649863709</v>
+        <v>37.02661972221967</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4075579860476507</v>
+        <v>0.2665010222509266</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-1.196920206963194</v>
+        <v>-0.3634513703988673</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>1256</v>
+        <v>1203</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>鮮活果汁-KY</t>
+          <t>味王</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>588.1096068583381</v>
+        <v>612.0062891595683</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>178</v>
+        <v>42.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45.859654796629</v>
+        <v>51.08312146663452</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>28.25635825628564</v>
+        <v>23.72536018186207</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.3109606858338057</v>
+        <v>0.7006289159568225</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-3.561089199197401</v>
+        <v>-0.1023070561293362</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>1326</v>
+        <v>1503</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>台化</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>586.5336044077791</v>
+        <v>609.0755798604765</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>48.8</v>
+        <v>220</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>50.13755224466051</v>
+        <v>52.3950742878724</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>22.1915170587878</v>
+        <v>24.90189653719466</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.653360440777913</v>
+        <v>0.4075579860476507</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.3172928979247058</v>
+        <v>-1.196920207344776</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>1514</v>
+        <v>1456</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>怡華</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>584.5308431950739</v>
+        <v>600.7028566477787</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>119.5</v>
+        <v>14.2</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>46.71686286221204</v>
+        <v>59.50271447829381</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>28.77011276907766</v>
+        <v>17.29317344978797</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4530843195073851</v>
+        <v>2.570285664777872</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-1.549849746020558</v>
+        <v>0.1438837593515702</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>1414</v>
+        <v>1110</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>東和</t>
+          <t>東泥</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>571.8464251455313</v>
+        <v>598.3004896690938</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>16.8</v>
+        <v>15.45</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>58.02488470573319</v>
+        <v>58.10218574887086</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>28.36879198857477</v>
+        <v>29.31634335065109</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.184642514553125</v>
+        <v>0.3300489669093865</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.2434468810550138</v>
+        <v>0.1071969358606779</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>1436</v>
+        <v>1560</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>華友聯</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>560.7872571453696</v>
+        <v>591.6735720442359</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>46.4</v>
+        <v>652</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.52710968011567</v>
+        <v>50.0804002833153</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>33.17138074989014</v>
+        <v>27.8853928867945</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.078725714536963</v>
+        <v>0.6673572044235961</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.3986082673342346</v>
+        <v>-14.95803493299846</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>1443</v>
+        <v>1525</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>立益</t>
+          <t>江申</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>558.1077874059225</v>
+        <v>577.9562333663105</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>26.7</v>
+        <v>65.2</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>60.04653730635702</v>
+        <v>48.95431695103694</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>14.01431601389977</v>
+        <v>27.96863902899001</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8107787405922549</v>
+        <v>0.2956233366310421</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>2</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0155706151827311</v>
+        <v>-0.3992823294640792</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>1504</v>
+        <v>1466</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>東元</t>
+          <t>聚隆</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>557.7620363517715</v>
+        <v>574.8338141547667</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>71</v>
+        <v>14.75</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,49 +3467,49 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>48.2371172265976</v>
+        <v>49.96145930350954</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>26.64561300253444</v>
+        <v>20.30768173687092</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2762036351771496</v>
+        <v>3.483381415476674</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.047308004111907</v>
+        <v>0.11166163617653</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>1466</v>
+        <v>1443</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>聚隆</t>
+          <t>立益</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>554.8338141547667</v>
+        <v>573.1077874059225</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>14.75</v>
+        <v>26.7</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>49.96145946716069</v>
+        <v>60.04653730131557</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.30768169959307</v>
+        <v>14.01431601095795</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>3.483381415476674</v>
+        <v>0.8107787405922549</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>0.1116616360715937</v>
+        <v>0.015570615192272</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>1535</v>
+        <v>1524</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>中宇</t>
+          <t>耿鼎</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>554.5173627512228</v>
+        <v>562.6390362926284</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>50.2</v>
+        <v>29.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.19809633984015</v>
+        <v>46.44727377951016</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.64389696551627</v>
+        <v>20.11195371816693</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.951736275122278</v>
+        <v>0.2639036292628381</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0599878909064518</v>
+        <v>-0.2775167757905613</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>1440</v>
+        <v>1413</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>南紡</t>
+          <t>宏洲</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>553.5749822816397</v>
+        <v>561.5605107125969</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>13.2</v>
+        <v>9.58</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>52.73572597749395</v>
+        <v>52.36503946393103</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>27.34557029402541</v>
+        <v>5.554012755154532</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3574982281639647</v>
+        <v>0.156051071259685</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0226672774177164</v>
+        <v>0.0065747186585948</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>1560</v>
+        <v>1517</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>利奇</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>551.6735720442359</v>
+        <v>557.3970858443415</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>652</v>
+        <v>10.35</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,49 +3679,49 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>50.08040027892002</v>
+        <v>51.65228891767234</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>27.88539280765612</v>
+        <v>22.17950629232972</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.6673572044235961</v>
+        <v>0.7397085844341441</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-14.95803493223524</v>
+        <v>0.0369620549814484</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>1108</v>
+        <v>1514</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>幸福</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>550.929976267976</v>
+        <v>554.5308431950739</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>13.8</v>
+        <v>119.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>46.34782246035204</v>
+        <v>46.71686288937001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>41.30554075981308</v>
+        <v>28.77011291221232</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5929976267976017</v>
+        <v>0.4530843195073851</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0349932672361587</v>
+        <v>-1.549849746631107</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>1525</v>
+        <v>1419</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>江申</t>
+          <t>新紡</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>537.9562333663105</v>
+        <v>551.0850226924246</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>65.2</v>
+        <v>65</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>48.95431695952313</v>
+        <v>50.83621208711004</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>27.96863892732801</v>
+        <v>19.3959037184171</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.2956233366310421</v>
+        <v>0.6085022692424537</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.3992823293686733</v>
+        <v>-0.1016944833211814</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>1419</v>
+        <v>1308</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>新紡</t>
+          <t>亞聚</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>531.0850226924246</v>
+        <v>537.6312016127026</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>65</v>
+        <v>13.65</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>50.83621212010239</v>
+        <v>48.40158776360459</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.39590379968413</v>
+        <v>15.46938890729059</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.6085022692424537</v>
+        <v>0.7631201612702651</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.1016944834070333</v>
+        <v>0.08422758449403089</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>1524</v>
+        <v>1324</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>耿鼎</t>
+          <t>地球</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>522.6390362926284</v>
+        <v>537.5129146166823</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>29.8</v>
+        <v>10.55</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>46.44727366679182</v>
+        <v>52.11450515991883</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.11195383075412</v>
+        <v>22.7948753523046</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2639036292628381</v>
+        <v>0.2512914616682338</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.2775167753803513</v>
+        <v>0.038510977717692</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>1324</v>
+        <v>1465</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>地球</t>
+          <t>偉全</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>517.5129146166823</v>
+        <v>527.7346755313573</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>10.55</v>
+        <v>12.4</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>52.11450509682006</v>
+        <v>53.97228935902353</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>22.7948751997872</v>
+        <v>18.35962603482061</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.2512914616682338</v>
+        <v>1.773467553135731</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0385109777558509</v>
+        <v>0.0095824821478555</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>1517</v>
+        <v>1535</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>利奇</t>
+          <t>中宇</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>517.3970858443415</v>
+        <v>524.5173627512228</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>10.35</v>
+        <v>50.2</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>51.65228883049777</v>
+        <v>51.19809641966016</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.1795062950746</v>
+        <v>21.64389701690356</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.7397085844341441</v>
+        <v>2.951736275122278</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0369620550291491</v>
+        <v>0.0599878907156541</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>1308</v>
+        <v>1440</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>亞聚</t>
+          <t>南紡</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>497.6312016127026</v>
+        <v>523.5749822816397</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>13.65</v>
+        <v>13.2</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.40158772580819</v>
+        <v>52.73572597031964</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.46938880550525</v>
+        <v>27.34557028232396</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.7631201612702651</v>
+        <v>0.3574982281639647</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.08422758453218999</v>
+        <v>0.0226672773986367</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>1540</v>
+        <v>1108</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>喬福</t>
+          <t>幸福</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>496.846755882321</v>
+        <v>520.929976267976</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>21.75</v>
+        <v>13.8</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>50.777010572287</v>
+        <v>46.34782241980042</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>20.81215875258377</v>
+        <v>41.30554082658099</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6846755882320936</v>
+        <v>0.5929976267976017</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.0165888425028077</v>
+        <v>0.034993267226619</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>1465</v>
+        <v>1540</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>偉全</t>
+          <t>喬福</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>487.7346755313573</v>
+        <v>506.846755882321</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>12.4</v>
+        <v>21.75</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>53.97228938734306</v>
+        <v>50.77701061818399</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.35962600348557</v>
+        <v>20.81215884088274</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.773467553135731</v>
+        <v>0.6846755882320936</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.009582482176474</v>
+        <v>-0.0165888426268226</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>1201</v>
+        <v>1453</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>味全</t>
+          <t>大將</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>481.225171037365</v>
+        <v>505.3948573572305</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>12.5</v>
+        <v>11.6</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>54.04686646300814</v>
+        <v>53.15526872691022</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>30.66397248138053</v>
+        <v>22.10246047519777</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.6225171037365032</v>
+        <v>1.039485735723049</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.061994092079511</v>
+        <v>0.0615961149199353</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4237,21 +4237,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>1109</v>
+        <v>1476</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>信大</t>
+          <t>儒鴻</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>480.96638300541</v>
+        <v>496.0818851119823</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>14.7</v>
+        <v>344.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,49 +4262,49 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45.06570090799431</v>
+        <v>50.11085064716731</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>31.15344408090204</v>
+        <v>13.27965434980241</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5966383005409999</v>
+        <v>0.6081885111982265</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0279807551230191</v>
+        <v>-0.1425862174824033</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>力鵬</t>
+          <t>宏益</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>480.8693676675126</v>
+        <v>495.2976581571236</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>6.15</v>
+        <v>10.95</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.31161623495407</v>
+        <v>52.37093338474356</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>38.57758003299209</v>
+        <v>22.04867831336666</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5869367667512565</v>
+        <v>0.5297658157123605</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0230809587647178</v>
+        <v>0.0672070613819052</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>1527</v>
+        <v>1474</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>鑽全</t>
+          <t>弘裕</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>479.7189713992496</v>
+        <v>493.4167801397038</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>33.25</v>
+        <v>10.2</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>55.43410980631234</v>
+        <v>53.99791279169264</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>18.72194714945789</v>
+        <v>29.22783063920179</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4718971399249608</v>
+        <v>0.3416780139703818</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0060573748507283</v>
+        <v>0.0214689272808564</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>1439</v>
+        <v>1529</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>雋揚</t>
+          <t>樂事綠能</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>476.6277048385154</v>
+        <v>490.8989006722297</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>25.6</v>
+        <v>23.1</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>50.72118104805784</v>
+        <v>54.01398867121794</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4.476519618812794</v>
+        <v>20.48784358808826</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.1627704838515403</v>
+        <v>0.5898900672229702</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.0060963547490598</v>
+        <v>0.123983589834915</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>1476</v>
+        <v>1201</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>儒鴻</t>
+          <t>味全</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>476.0818851119823</v>
+        <v>481.225171037365</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>344.5</v>
+        <v>12.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,49 +4474,49 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.11085056032451</v>
+        <v>54.04686638878186</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>13.27965421644767</v>
+        <v>30.66397234786397</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6081885111982265</v>
+        <v>0.6225171037365032</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1425862154790478</v>
+        <v>0.0619940920604318</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>1474</v>
+        <v>1418</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>弘裕</t>
+          <t>東華</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>473.4167801397038</v>
+        <v>478.5111209894368</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>10.2</v>
+        <v>18.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>53.99791271560029</v>
+        <v>49.4664930633929</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>29.22783063607494</v>
+        <v>22.80060001926421</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.3416780139703818</v>
+        <v>1.851112098943678</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.0214689273190139</v>
+        <v>0.0271783929029705</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>1453</v>
+        <v>1338</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>大將</t>
+          <t>廣華-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>470.3948573572305</v>
+        <v>474.08392019742</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>11.6</v>
+        <v>16.7</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.15526862288156</v>
+        <v>54.60403234627347</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>22.10246033275705</v>
+        <v>19.40182446104368</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.039485735723049</v>
+        <v>1.908392019741997</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0615961149962546</v>
+        <v>0.0422283830212851</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>1217</v>
+        <v>1454</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>愛之味</t>
+          <t>台富</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>455.2343406311314</v>
+        <v>473.8571373061254</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>9.869999999999999</v>
+        <v>13.05</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>54.9273473320075</v>
+        <v>50.66332166053918</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>25.64288877876004</v>
+        <v>26.59923091914078</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.523434063113138</v>
+        <v>0.3857137306125377</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0341410452120482</v>
+        <v>0.0309507408667718</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4661,21 +4661,21 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>1338</v>
+        <v>1312</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>廣華-KY</t>
+          <t>國喬</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>454.08392019742</v>
+        <v>464.3261479491456</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>16.7</v>
+        <v>12.95</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>54.60403229879577</v>
+        <v>54.64906871932152</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.40182444505401</v>
+        <v>32.69837900729379</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.908392019741997</v>
+        <v>0.4326147949145615</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>1</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.042228383059441</v>
+        <v>0.1589394685624287</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>1454</v>
+        <v>1109</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>台富</t>
+          <t>信大</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>453.8571373061254</v>
+        <v>450.96638300541</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>13.05</v>
+        <v>14.7</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>50.66332167220298</v>
+        <v>45.06570085420536</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>26.59923103189208</v>
+        <v>31.15344404167594</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.3857137306125377</v>
+        <v>0.5966383005409999</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.0309507408286112</v>
+        <v>0.027980755103939</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>1529</v>
+        <v>1447</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>樂事綠能</t>
+          <t>力鵬</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>450.8989006722297</v>
+        <v>450.8693676675126</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>23.1</v>
+        <v>6.15</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>54.01398855081769</v>
+        <v>53.31161624366101</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20.4878435256088</v>
+        <v>38.5775800774903</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5898900672229702</v>
+        <v>0.5869367667512565</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.123983589968467</v>
+        <v>-0.02308095878189</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>1417</v>
+        <v>1527</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>嘉裕</t>
+          <t>鑽全</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>446.6671060962032</v>
+        <v>449.7189713992496</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>8.49</v>
+        <v>33.25</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>53.1226803594906</v>
+        <v>55.43410996739598</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>23.16178450345907</v>
+        <v>18.72194719285022</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.166710609620316</v>
+        <v>0.4718971399249608</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>1</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0496140805722256</v>
+        <v>0.0060573746885548</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>1312</v>
+        <v>1439</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>國喬</t>
+          <t>雋揚</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>444.3261479491456</v>
+        <v>446.6277048385154</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>12.95</v>
+        <v>25.6</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>54.64906867114912</v>
+        <v>50.72118104505813</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>32.69837898274136</v>
+        <v>4.476519618812796</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4326147949145615</v>
+        <v>0.1627704838515403</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,11 +4916,11 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1589394685624287</v>
+        <v>-0.0060963547490598</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.45564681291501</v>
+        <v>50.45564679592734</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>18.45171660324862</v>
+        <v>18.4517165786143</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.6324567469813157</v>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>1452</v>
+        <v>1213</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>宏益</t>
+          <t>大飲</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>440.2976581571236</v>
+        <v>432.8753243026745</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>10.95</v>
+        <v>8.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>52.37093324033624</v>
+        <v>51.76984747321264</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>22.04867818845561</v>
+        <v>10.1947708206489</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.5297658157123605</v>
+        <v>0.7875324302674526</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0672070614391421</v>
+        <v>0.143568135392418</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>東華</t>
+          <t>嘉裕</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>438.5111209894368</v>
+        <v>431.6671060962032</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>18.5</v>
+        <v>8.49</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>49.46649303816449</v>
+        <v>53.12268039375399</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>22.80060000065392</v>
+        <v>23.1617844326598</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.851112098943678</v>
+        <v>1.166710609620316</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0271783929983691</v>
+        <v>0.0496140805588684</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>1516</v>
+        <v>1217</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>川飛</t>
+          <t>愛之味</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>428.9632206232792</v>
+        <v>425.2343406311314</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>21.5</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>53.28549248846954</v>
+        <v>54.9273473320075</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>16.49282472936422</v>
+        <v>25.64288875802795</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.3963220623279205</v>
+        <v>0.523434063113138</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0437959827572071</v>
+        <v>0.0341410452025087</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>1528</v>
+        <v>1522</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>恩德</t>
+          <t>堤維西</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>423.4166307222619</v>
+        <v>423.6232744970214</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>25.25</v>
+        <v>31.05</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>44.49103103406176</v>
+        <v>48.09251493939554</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>11.31847829392866</v>
+        <v>20.54785072023609</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3416630722261854</v>
+        <v>0.3623274497021437</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.2335350500568887</v>
+        <v>0.0056255377189296</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>1457</v>
+        <v>1215</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>宜進</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>406.0684683155664</v>
+        <v>423.3531910046675</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>14.55</v>
+        <v>118</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>50.78804576905039</v>
+        <v>33.43798515005278</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>21.6588313457788</v>
+        <v>40.68071773525183</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6068468315566414</v>
+        <v>0.3353191004667516</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0475030549413106</v>
+        <v>-0.5541347520163544</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>1526</v>
+        <v>1536</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>日馳</t>
+          <t>和大</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>405.4584147842329</v>
+        <v>418.4142898472237</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>14.45</v>
+        <v>49</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>40.22844764088763</v>
+        <v>43.32041648591657</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>23.13609484687827</v>
+        <v>13.68511765468888</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5458414784232883</v>
+        <v>0.3414289847223687</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0315771217367702</v>
+        <v>-0.2964371716070462</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>1539</v>
+        <v>1464</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>巨庭</t>
+          <t>得力</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>404.5638929542776</v>
+        <v>413.7170281326266</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>15.8</v>
+        <v>10.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>45.76105289383783</v>
+        <v>54.19099890500168</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>22.21761114403517</v>
+        <v>22.76290071193142</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4563892954277528</v>
+        <v>0.8717028132626645</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.0280002995712067</v>
+        <v>0.0096852273749191</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>1582</v>
+        <v>1457</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>信錦</t>
+          <t>宜進</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>404.4222439440006</v>
+        <v>406.0684683155664</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>94.90000000000001</v>
+        <v>14.55</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>43.2549990511823</v>
+        <v>50.788045845173</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>25.0394416846638</v>
+        <v>21.65883123859198</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4422243944000618</v>
+        <v>0.6068468315566414</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-2.924970141122248</v>
+        <v>0.0475030549031525</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>1215</v>
+        <v>1472</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>三洋實業</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>403.3531910046675</v>
+        <v>404.3812034942693</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>118</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,49 +5428,49 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>33.43798514545767</v>
+        <v>51.89808106564344</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>40.68071772939203</v>
+        <v>10.94982778984992</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.3353191004667516</v>
+        <v>0.4381203494269262</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.5541347518827964</v>
+        <v>0.5961935336377331</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>1467</v>
+        <v>1402</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>南緯</t>
+          <t>遠東新</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>400.0328723040545</v>
+        <v>399.0620337406089</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>7.5</v>
+        <v>27</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>54.88111871890912</v>
+        <v>52.57565831300547</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>31.79915625088173</v>
+        <v>17.55582869246847</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5032872304054471</v>
+        <v>0.4062033740608849</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.032284372879063</v>
+        <v>0.1344095298635527</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>1218</v>
+        <v>1516</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>泰山</t>
+          <t>川飛</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>394.3259529204953</v>
+        <v>398.9632206232792</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>18</v>
+        <v>21.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>31.42565455077136</v>
+        <v>53.28549252812449</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.87768239776575</v>
+        <v>16.49282475096546</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2.43259529204953</v>
+        <v>0.3963220623279205</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0427541953863107</v>
+        <v>0.0437959827190479</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>得力</t>
+          <t>聯發</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>393.7170281326266</v>
+        <v>394.4698789227649</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>54.19099856303868</v>
+        <v>54.07474234952175</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>22.76290059803477</v>
+        <v>20.32042608944945</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8717028132626645</v>
+        <v>0.4469878922764926</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0096852274798557</v>
+        <v>0.0125810027095239</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>1522</v>
+        <v>1218</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>堤維西</t>
+          <t>泰山</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>383.6232744970214</v>
+        <v>394.3259529204953</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>31.05</v>
+        <v>18</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>48.09251486501826</v>
+        <v>31.42565453414352</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.54785066615853</v>
+        <v>23.8776822863353</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.3623274497021437</v>
+        <v>2.43259529204953</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.00562553805282</v>
+        <v>-0.0427541953767708</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>1459</v>
+        <v>1528</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>聯發</t>
+          <t>恩德</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>379.4698789227649</v>
+        <v>393.4166307222619</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>11.8</v>
+        <v>25.25</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>54.07474203727521</v>
+        <v>44.49103105105035</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>20.32042568421653</v>
+        <v>11.31847846218443</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4469878922764926</v>
+        <v>0.3416630722261854</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.012581002776303</v>
+        <v>-0.2335350501522849</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>1536</v>
+        <v>1301</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>和大</t>
+          <t>台塑</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>378.4142898472237</v>
+        <v>392.3329936414336</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>49</v>
+        <v>45.25</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>43.32041640152971</v>
+        <v>43.01734878465505</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>13.68511749171744</v>
+        <v>21.91502079597618</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.3414289847223687</v>
+        <v>0.7332993641433647</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>1</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.2964371709583451</v>
+        <v>-0.31144674289037</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>1213</v>
+        <v>1467</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>大飲</t>
+          <t>南緯</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>377.8753243026745</v>
+        <v>385.0328723040545</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.76984744798086</v>
+        <v>54.88111880591977</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.19477082053214</v>
+        <v>31.79915697137705</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7875324302674526</v>
+        <v>0.5032872304054471</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.1435681355259757</v>
+        <v>0.0322843728771548</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>1301</v>
+        <v>1315</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>台塑</t>
+          <t>達新</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>372.3329936414336</v>
+        <v>381.029688370797</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>45.25</v>
+        <v>61.2</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.01734874941964</v>
+        <v>44.71170180608961</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>21.91502072095989</v>
+        <v>15.09951779121607</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7332993641433647</v>
+        <v>0.6029688370796954</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.3114467427281939</v>
+        <v>0.0248883995381749</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>1519</v>
+        <v>1526</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>日馳</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>364.9248917273338</v>
+        <v>375.4584147842329</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>791</v>
+        <v>14.45</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.54322785979619</v>
+        <v>40.22844775097894</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>12.73326610977132</v>
+        <v>23.13609488295682</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.4924891727333839</v>
+        <v>0.5458414784232883</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-8.055425576722198</v>
+        <v>0.031577121622296</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>1472</v>
+        <v>1539</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>三洋實業</t>
+          <t>巨庭</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>364.3812034942693</v>
+        <v>374.5638929542776</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>15.8</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>51.89808102311575</v>
+        <v>45.76105306380876</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>10.94982762298062</v>
+        <v>22.21761121545794</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4381203494269262</v>
+        <v>0.4563892954277528</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.5961935343055347</v>
+        <v>-0.0280002996856832</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>1451</v>
+        <v>1582</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>年興</t>
+          <t>信錦</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>362.56433797689</v>
+        <v>374.4222439440006</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>16.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.20791894152574</v>
+        <v>43.25499905226678</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>13.89501399742032</v>
+        <v>25.0394416413595</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.2564337976889988</v>
+        <v>0.4422243944000618</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0265035133030491</v>
+        <v>-2.924970141427516</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>1315</v>
+        <v>1323</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>達新</t>
+          <t>永裕</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>361.029688370797</v>
+        <v>373.8338345854459</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>61.2</v>
+        <v>19.8</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>44.71170183033281</v>
+        <v>46.24220138660446</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>15.09951772260936</v>
+        <v>12.5870695587481</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6029688370796954</v>
+        <v>1.383383458544588</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0248883995572519</v>
+        <v>-0.0538628342336294</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>1304</v>
+        <v>1519</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>台聚</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>360.3407508218997</v>
+        <v>364.9248917273338</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>12.7</v>
+        <v>791</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>46.4699188220925</v>
+        <v>42.54322786128419</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>18.98984478829673</v>
+        <v>12.73326620950612</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5340750821899689</v>
+        <v>0.4924891727333839</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.0486844116046792</v>
+        <v>-8.055425578153155</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>1558</v>
+        <v>1304</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>伸興</t>
+          <t>台聚</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>355.4676300095698</v>
+        <v>360.3407508218997</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>90.40000000000001</v>
+        <v>12.7</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>44.8530732070111</v>
+        <v>46.46991886700134</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>12.21557569259792</v>
+        <v>18.98984475558217</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.5467630009569782</v>
+        <v>0.5340750821899689</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.0255344379153663</v>
+        <v>0.0486844115703352</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>1323</v>
+        <v>1558</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>永裕</t>
+          <t>伸興</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>353.8338345854459</v>
+        <v>355.4676300095698</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>19.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.24220138660446</v>
+        <v>44.85307321604426</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>12.58706945358488</v>
+        <v>12.21557579324959</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.383383458544588</v>
+        <v>0.5467630009569782</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0538628342336294</v>
+        <v>-0.0255344381634008</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>1402</v>
+        <v>1515</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>遠東新</t>
+          <t>力山</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>344.0620337406089</v>
+        <v>343.51357391027</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>27</v>
+        <v>23.35</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>52.57565824396448</v>
+        <v>51.6179679442076</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.55582863742647</v>
+        <v>20.31693515716493</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4062033740608849</v>
+        <v>0.3513573910269998</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,11 +6294,11 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1344095299589499</v>
+        <v>0.0665139701426056</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>37.8375172309057</v>
+        <v>37.83751721194832</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>33.10296921636817</v>
+        <v>33.10296917671001</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.6501877487792124</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.0207467499729693</v>
+        <v>0.0207467499634284</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>1515</v>
+        <v>1305</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>力山</t>
+          <t>華夏</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>323.51357391027</v>
+        <v>341.0089866782794</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>23.35</v>
+        <v>12.65</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>51.61796798235566</v>
+        <v>44.98730759138216</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>20.3169351950965</v>
+        <v>13.53928759088452</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3513573910269998</v>
+        <v>0.600898667827945</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.06651397033339911</v>
+        <v>0.0658213453842426</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>1541</v>
+        <v>1521</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>錩泰</t>
+          <t>大億</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>318.4707370362703</v>
+        <v>339.9454873652118</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>20.8</v>
+        <v>25.95</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>39.48832896798056</v>
+        <v>49.11580849373478</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>12.77523155861883</v>
+        <v>19.28508312105867</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3470737036270277</v>
+        <v>0.994548736521174</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,11 +6453,11 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0425908990370097</v>
+        <v>-0.1479025256076265</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>317.9222869198932</v>
+        <v>332.9222869198932</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>27.8</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>43.37616879551138</v>
+        <v>43.37616877704109</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>23.17412425837933</v>
+        <v>23.17412419904106</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>0.2922286919893188</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.0284437961204169</v>
+        <v>0.0284437960822583</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>1305</v>
+        <v>1451</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>華夏</t>
+          <t>年興</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>301.0089866782794</v>
+        <v>332.56433797689</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>12.65</v>
+        <v>16.7</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.98730756965236</v>
+        <v>48.207918852186</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>13.53928751307989</v>
+        <v>13.89501403282181</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.600898667827945</v>
+        <v>0.2564337976889988</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>1</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0658213454224022</v>
+        <v>0.0265035133125908</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>1521</v>
+        <v>1416</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>大億</t>
+          <t>廣豐</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>299.9454873652118</v>
+        <v>317.8948418405161</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>25.95</v>
+        <v>11.05</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>49.11580854569841</v>
+        <v>42.11014216653053</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>19.28508318584197</v>
+        <v>31.80188259303876</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.994548736521174</v>
+        <v>1.289484184051608</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>1</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.1479025256553262</v>
+        <v>-0.0300436003057469</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>1468</v>
+        <v>1541</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>昶和</t>
+          <t>錩泰</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>295.5384491281132</v>
+        <v>288.4707370362703</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>11.9</v>
+        <v>20.8</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>45.45932766250115</v>
+        <v>39.48832900758074</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>10.82806541051927</v>
+        <v>12.77523165070734</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.053844912811322</v>
+        <v>0.3470737036270277</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>2</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0282654076159391</v>
+        <v>0.0425908989320721</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>1470</v>
+        <v>1410</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>大統新創</t>
+          <t>南染</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>295</v>
+        <v>287.9717251895773</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>15.67855126022692</v>
+        <v>31.71589914974973</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>7.728652171961174</v>
+        <v>12.73460790662306</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0</v>
+        <v>1.797172518957734</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-1.435743090420541</v>
+        <v>-0.0066024753152883</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>1325</v>
+        <v>1468</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>恆大</t>
+          <t>昶和</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>291.7991155989504</v>
+        <v>265.5384491281132</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>26.25</v>
+        <v>11.9</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>44.80029307696225</v>
+        <v>45.45932761779794</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>13.47752484361214</v>
+        <v>10.82806557186034</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.679911559895044</v>
+        <v>1.053844912811322</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0804573260825234</v>
+        <v>-0.0282654076254778</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>1309</v>
+        <v>1470</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>台達化</t>
+          <t>大統新創</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>284.3985292705369</v>
+        <v>265</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>15.05</v>
+        <v>0</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>40.61961309532357</v>
+        <v>15.67855110464905</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12.19515297908055</v>
+        <v>7.72865217623735</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.439852927053687</v>
+        <v>0</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0037086390095349</v>
+        <v>-1.435743090420541</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>1416</v>
+        <v>1512</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>廣豐</t>
+          <t>瑞利</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>277.8948418405161</v>
+        <v>262.5340702143696</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>11.05</v>
+        <v>6.86</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>42.11014220369474</v>
+        <v>44.0374222114027</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>31.80188256085782</v>
+        <v>10.84296064564483</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.289484184051608</v>
+        <v>0.7534070214369648</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.0300436002962067</v>
+        <v>0.004764420478709</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>1512</v>
+        <v>1325</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>瑞利</t>
+          <t>恆大</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>262.5340702143696</v>
+        <v>261.7991155989504</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>6.86</v>
+        <v>26.25</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.03742220717348</v>
+        <v>44.80029306325223</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>10.84296063531815</v>
+        <v>13.4775248890724</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.7534070214369648</v>
+        <v>0.679911559895044</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.0047644204806166</v>
+        <v>-0.0804573261302209</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>台苯</t>
+          <t>台達化</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>250.1384772189957</v>
+        <v>254.3985292705369</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>8.539999999999999</v>
+        <v>15.05</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>47.55053654382681</v>
+        <v>40.61961315238608</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>23.31603427815794</v>
+        <v>12.19515299548365</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5138477218995723</v>
+        <v>0.439852927053687</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>1</v>
@@ -6983,51 +6983,51 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0754202665409697</v>
+        <v>0.003708638933216</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>1410</v>
+        <v>1435</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>南染</t>
+          <t>中福</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>247.9717251895773</v>
+        <v>235.744744632218</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>24.8</v>
+        <v>5.36</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G124" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>31.71589922553389</v>
+        <v>44.34023690628555</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>12.73460784812295</v>
+        <v>8.19264734328088</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.797172518957734</v>
+        <v>1.574474463221793</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0066024752962093</v>
+        <v>-0.352936500874162</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>1340</v>
+        <v>1569</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>勝悅-KY</t>
+          <t>濱川</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>239.9987465796281</v>
+        <v>235.5260915412503</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>5.64</v>
+        <v>48.55</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>48.66067854642586</v>
+        <v>39.03396409102874</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>19.19431529567385</v>
+        <v>13.86624536206898</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4998746579628078</v>
+        <v>0.5526091541250258</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,51 +7089,51 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0335620635008884</v>
+        <v>-0.31049684750506</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>1435</v>
+        <v>1310</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>中福</t>
+          <t>台苯</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>235.744744632218</v>
+        <v>220.1384772189957</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>5.36</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G126" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>44.34023105610312</v>
+        <v>47.5505366190208</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>8.192646265935108</v>
+        <v>23.31603433902545</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.574474463221793</v>
+        <v>0.5138477218995723</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.3529364444291258</v>
+        <v>0.0754202664913623</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>1569</v>
+        <v>1340</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>濱川</t>
+          <t>勝悅-KY</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>235.5260915412503</v>
+        <v>209.9987465796281</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>48.55</v>
+        <v>5.64</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,16 +7177,16 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>39.03396396580733</v>
+        <v>48.66067857430797</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>13.86624521651145</v>
+        <v>19.19431532759825</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.5526091541250258</v>
+        <v>0.4998746579628078</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7195,31 +7195,31 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-0.3104968465415507</v>
+        <v>0.0335620634722694</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>1220</v>
+        <v>1441</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>台榮</t>
+          <t>大東</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>195.8711738852217</v>
+        <v>180.3619808143488</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>11.65</v>
+        <v>9.19</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>34.69467433027302</v>
+        <v>39.7749298029973</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>30.36688556988454</v>
+        <v>13.77744182568732</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5871173885221729</v>
+        <v>1.036198081434876</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,31 +7248,31 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.0059752695110183</v>
+        <v>0.0068182378901363</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>1441</v>
+        <v>1473</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>大東</t>
+          <t>台南</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>180.3619808143488</v>
+        <v>178.1528234365003</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>9.19</v>
+        <v>20.5</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,13 +7283,13 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>39.77492973194173</v>
+        <v>41.55928962176637</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>13.77744189540488</v>
+        <v>24.85643470801838</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.036198081434876</v>
+        <v>0.3152823436500249</v>
       </c>
       <c r="K129" s="2" t="n">
         <v>0</v>
@@ -7301,31 +7301,31 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>0.0068182378901363</v>
+        <v>0.0356361179913519</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>1473</v>
+        <v>1220</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>台南</t>
+          <t>台榮</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>178.1528234365003</v>
+        <v>165.8711738852217</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>20.5</v>
+        <v>11.65</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
@@ -7336,13 +7336,13 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>41.55928959569001</v>
+        <v>34.69467435655912</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>24.85643469397225</v>
+        <v>30.36688552377055</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.3152823436500249</v>
+        <v>0.5871173885221729</v>
       </c>
       <c r="K130" s="2" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.0356361181058308</v>
+        <v>0.0059752694919389</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>166.0675370882175</v>
+        <v>136.0675370882175</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>11.7</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>51.60683373536176</v>
+        <v>51.60683373688833</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>5.877352800637008</v>
+        <v>5.877352865346669</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.6067537088217542</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>-0.0473987737842043</v>
+        <v>-0.0473987737365049</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>154.9929581507737</v>
+        <v>124.9929581507737</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>10.7</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>44.05474947378519</v>
+        <v>44.05474950697254</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>16.19819190287276</v>
+        <v>16.19819190009964</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.4992958150773687</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.0213066230505422</v>
+        <v>-0.0213066231344921</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>100.4127312925289</v>
+        <v>70.4127312925289</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>11.15</v>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>33.22905734527777</v>
+        <v>33.22905751570994</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>11.93134605606362</v>
+        <v>11.93134629028021</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>1.041273129252891</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.0073494239968716</v>
+        <v>-0.0073494241685853</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
